--- a/raw/processedSamples/20260512_r3_SG_USDA-Blood_RT-QuIC.xlsx
+++ b/raw/processedSamples/20260512_r3_SG_USDA-Blood_RT-QuIC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MNPRO\Desktop\RT-QuIC Data\Sarah's RT-QuIC Data\2026\20260512_r3_SG_USDA-Blood_RT-QuIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BC1DA8D-A3CC-4718-968F-DD0D8690C982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847C10FA-9E23-48DB-9D1F-09980FAA38E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5130" yWindow="540" windowWidth="21600" windowHeight="13980" xr2:uid="{7BAF1EBB-F217-431A-8482-EF30A0548043}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BAF1EBB-F217-431A-8482-EF30A0548043}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -2015,37 +2015,37 @@
         <v>1000</v>
       </c>
       <c r="C38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="D38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="H38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="K38" s="12">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="L38" s="12">
-        <v>100</v>
-      </c>
-      <c r="M38" s="13">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="M38" s="12">
+        <v>4</v>
       </c>
       <c r="O38" s="21"/>
     </row>
@@ -2056,38 +2056,38 @@
       <c r="B39" s="5">
         <v>1000</v>
       </c>
-      <c r="C39" s="14">
-        <v>100</v>
-      </c>
-      <c r="D39" s="14">
-        <v>100</v>
-      </c>
-      <c r="E39" s="14">
-        <v>100</v>
-      </c>
-      <c r="F39" s="14">
-        <v>100</v>
-      </c>
-      <c r="G39" s="14">
-        <v>100</v>
-      </c>
-      <c r="H39" s="14">
-        <v>100</v>
-      </c>
-      <c r="I39" s="14">
-        <v>100</v>
-      </c>
-      <c r="J39" s="14">
-        <v>100</v>
-      </c>
-      <c r="K39" s="14">
-        <v>100</v>
-      </c>
-      <c r="L39" s="14">
-        <v>100</v>
-      </c>
-      <c r="M39" s="15">
-        <v>100</v>
+      <c r="C39" s="12">
+        <v>4</v>
+      </c>
+      <c r="D39" s="12">
+        <v>4</v>
+      </c>
+      <c r="E39" s="12">
+        <v>4</v>
+      </c>
+      <c r="F39" s="12">
+        <v>4</v>
+      </c>
+      <c r="G39" s="12">
+        <v>4</v>
+      </c>
+      <c r="H39" s="12">
+        <v>4</v>
+      </c>
+      <c r="I39" s="12">
+        <v>4</v>
+      </c>
+      <c r="J39" s="12">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12">
+        <v>4</v>
+      </c>
+      <c r="L39" s="12">
+        <v>4</v>
+      </c>
+      <c r="M39" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -2097,38 +2097,38 @@
       <c r="B40" s="5">
         <v>1000</v>
       </c>
-      <c r="C40" s="14">
-        <v>100</v>
-      </c>
-      <c r="D40" s="14">
-        <v>100</v>
-      </c>
-      <c r="E40" s="14">
-        <v>100</v>
-      </c>
-      <c r="F40" s="14">
-        <v>100</v>
-      </c>
-      <c r="G40" s="14">
-        <v>100</v>
-      </c>
-      <c r="H40" s="14">
-        <v>100</v>
-      </c>
-      <c r="I40" s="14">
-        <v>100</v>
-      </c>
-      <c r="J40" s="14">
-        <v>100</v>
-      </c>
-      <c r="K40" s="14">
-        <v>100</v>
-      </c>
-      <c r="L40" s="14">
-        <v>100</v>
-      </c>
-      <c r="M40" s="15">
-        <v>100</v>
+      <c r="C40" s="12">
+        <v>4</v>
+      </c>
+      <c r="D40" s="12">
+        <v>4</v>
+      </c>
+      <c r="E40" s="12">
+        <v>4</v>
+      </c>
+      <c r="F40" s="12">
+        <v>4</v>
+      </c>
+      <c r="G40" s="12">
+        <v>4</v>
+      </c>
+      <c r="H40" s="12">
+        <v>4</v>
+      </c>
+      <c r="I40" s="12">
+        <v>4</v>
+      </c>
+      <c r="J40" s="12">
+        <v>4</v>
+      </c>
+      <c r="K40" s="12">
+        <v>4</v>
+      </c>
+      <c r="L40" s="12">
+        <v>4</v>
+      </c>
+      <c r="M40" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -2138,38 +2138,38 @@
       <c r="B41" s="5">
         <v>1000</v>
       </c>
-      <c r="C41" s="14">
-        <v>100</v>
-      </c>
-      <c r="D41" s="14">
-        <v>100</v>
-      </c>
-      <c r="E41" s="14">
-        <v>100</v>
-      </c>
-      <c r="F41" s="14">
-        <v>100</v>
-      </c>
-      <c r="G41" s="14">
-        <v>100</v>
-      </c>
-      <c r="H41" s="14">
-        <v>100</v>
-      </c>
-      <c r="I41" s="14">
-        <v>100</v>
-      </c>
-      <c r="J41" s="14">
-        <v>100</v>
-      </c>
-      <c r="K41" s="14">
-        <v>100</v>
-      </c>
-      <c r="L41" s="14">
-        <v>100</v>
-      </c>
-      <c r="M41" s="15">
-        <v>100</v>
+      <c r="C41" s="12">
+        <v>4</v>
+      </c>
+      <c r="D41" s="12">
+        <v>4</v>
+      </c>
+      <c r="E41" s="12">
+        <v>4</v>
+      </c>
+      <c r="F41" s="12">
+        <v>4</v>
+      </c>
+      <c r="G41" s="12">
+        <v>4</v>
+      </c>
+      <c r="H41" s="12">
+        <v>4</v>
+      </c>
+      <c r="I41" s="12">
+        <v>4</v>
+      </c>
+      <c r="J41" s="12">
+        <v>4</v>
+      </c>
+      <c r="K41" s="12">
+        <v>4</v>
+      </c>
+      <c r="L41" s="12">
+        <v>4</v>
+      </c>
+      <c r="M41" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2179,38 +2179,38 @@
       <c r="B42" s="5">
         <v>1000</v>
       </c>
-      <c r="C42" s="14">
-        <v>100</v>
-      </c>
-      <c r="D42" s="14">
-        <v>100</v>
-      </c>
-      <c r="E42" s="14">
-        <v>100</v>
-      </c>
-      <c r="F42" s="14">
-        <v>100</v>
-      </c>
-      <c r="G42" s="14">
-        <v>100</v>
-      </c>
-      <c r="H42" s="14">
-        <v>100</v>
-      </c>
-      <c r="I42" s="14">
-        <v>100</v>
-      </c>
-      <c r="J42" s="14">
-        <v>100</v>
-      </c>
-      <c r="K42" s="14">
-        <v>100</v>
-      </c>
-      <c r="L42" s="14">
-        <v>100</v>
-      </c>
-      <c r="M42" s="15">
-        <v>100</v>
+      <c r="C42" s="12">
+        <v>4</v>
+      </c>
+      <c r="D42" s="12">
+        <v>4</v>
+      </c>
+      <c r="E42" s="12">
+        <v>4</v>
+      </c>
+      <c r="F42" s="12">
+        <v>4</v>
+      </c>
+      <c r="G42" s="12">
+        <v>4</v>
+      </c>
+      <c r="H42" s="12">
+        <v>4</v>
+      </c>
+      <c r="I42" s="12">
+        <v>4</v>
+      </c>
+      <c r="J42" s="12">
+        <v>4</v>
+      </c>
+      <c r="K42" s="12">
+        <v>4</v>
+      </c>
+      <c r="L42" s="12">
+        <v>4</v>
+      </c>
+      <c r="M42" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2220,38 +2220,38 @@
       <c r="B43" s="5">
         <v>1000</v>
       </c>
-      <c r="C43" s="14">
-        <v>100</v>
-      </c>
-      <c r="D43" s="14">
-        <v>100</v>
-      </c>
-      <c r="E43" s="14">
-        <v>100</v>
-      </c>
-      <c r="F43" s="14">
-        <v>100</v>
-      </c>
-      <c r="G43" s="14">
-        <v>100</v>
-      </c>
-      <c r="H43" s="14">
-        <v>100</v>
-      </c>
-      <c r="I43" s="14">
-        <v>100</v>
-      </c>
-      <c r="J43" s="14">
-        <v>100</v>
-      </c>
-      <c r="K43" s="14">
-        <v>100</v>
-      </c>
-      <c r="L43" s="14">
-        <v>100</v>
-      </c>
-      <c r="M43" s="15">
-        <v>100</v>
+      <c r="C43" s="12">
+        <v>4</v>
+      </c>
+      <c r="D43" s="12">
+        <v>4</v>
+      </c>
+      <c r="E43" s="12">
+        <v>4</v>
+      </c>
+      <c r="F43" s="12">
+        <v>4</v>
+      </c>
+      <c r="G43" s="12">
+        <v>4</v>
+      </c>
+      <c r="H43" s="12">
+        <v>4</v>
+      </c>
+      <c r="I43" s="12">
+        <v>4</v>
+      </c>
+      <c r="J43" s="12">
+        <v>4</v>
+      </c>
+      <c r="K43" s="12">
+        <v>4</v>
+      </c>
+      <c r="L43" s="12">
+        <v>4</v>
+      </c>
+      <c r="M43" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2261,38 +2261,38 @@
       <c r="B44" s="5">
         <v>1000</v>
       </c>
-      <c r="C44" s="14">
-        <v>100</v>
-      </c>
-      <c r="D44" s="14">
-        <v>100</v>
-      </c>
-      <c r="E44" s="14">
-        <v>100</v>
-      </c>
-      <c r="F44" s="14">
-        <v>100</v>
-      </c>
-      <c r="G44" s="14">
-        <v>100</v>
-      </c>
-      <c r="H44" s="14">
-        <v>100</v>
-      </c>
-      <c r="I44" s="14">
-        <v>100</v>
-      </c>
-      <c r="J44" s="14">
-        <v>100</v>
-      </c>
-      <c r="K44" s="14">
-        <v>100</v>
-      </c>
-      <c r="L44" s="14">
-        <v>100</v>
-      </c>
-      <c r="M44" s="15">
-        <v>100</v>
+      <c r="C44" s="12">
+        <v>4</v>
+      </c>
+      <c r="D44" s="12">
+        <v>4</v>
+      </c>
+      <c r="E44" s="12">
+        <v>4</v>
+      </c>
+      <c r="F44" s="12">
+        <v>4</v>
+      </c>
+      <c r="G44" s="12">
+        <v>4</v>
+      </c>
+      <c r="H44" s="12">
+        <v>4</v>
+      </c>
+      <c r="I44" s="12">
+        <v>4</v>
+      </c>
+      <c r="J44" s="12">
+        <v>4</v>
+      </c>
+      <c r="K44" s="12">
+        <v>4</v>
+      </c>
+      <c r="L44" s="12">
+        <v>4</v>
+      </c>
+      <c r="M44" s="12">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -2302,38 +2302,38 @@
       <c r="B45" s="16">
         <v>1000</v>
       </c>
-      <c r="C45" s="17">
-        <v>100</v>
-      </c>
-      <c r="D45" s="17">
-        <v>100</v>
-      </c>
-      <c r="E45" s="17">
-        <v>100</v>
-      </c>
-      <c r="F45" s="17">
-        <v>100</v>
-      </c>
-      <c r="G45" s="17">
-        <v>100</v>
-      </c>
-      <c r="H45" s="17">
-        <v>100</v>
-      </c>
-      <c r="I45" s="17">
-        <v>100</v>
-      </c>
-      <c r="J45" s="17">
-        <v>100</v>
-      </c>
-      <c r="K45" s="17">
-        <v>100</v>
-      </c>
-      <c r="L45" s="17">
-        <v>100</v>
-      </c>
-      <c r="M45" s="18">
-        <v>100</v>
+      <c r="C45" s="12">
+        <v>4</v>
+      </c>
+      <c r="D45" s="12">
+        <v>4</v>
+      </c>
+      <c r="E45" s="12">
+        <v>4</v>
+      </c>
+      <c r="F45" s="12">
+        <v>4</v>
+      </c>
+      <c r="G45" s="12">
+        <v>4</v>
+      </c>
+      <c r="H45" s="12">
+        <v>4</v>
+      </c>
+      <c r="I45" s="12">
+        <v>4</v>
+      </c>
+      <c r="J45" s="12">
+        <v>4</v>
+      </c>
+      <c r="K45" s="12">
+        <v>4</v>
+      </c>
+      <c r="L45" s="12">
+        <v>4</v>
+      </c>
+      <c r="M45" s="12">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
